--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,16 +105,16 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PersonneStructure</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-assigned-entity</t>
-  </si>
-  <si>
-    <t>PersonneStructure</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-assigned-entity</t>
+  </si>
+  <si>
+    <t>FRLMPersonneStructure</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -123,91 +123,91 @@
     <t>assignedEntity</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.identifiantPersonne</t>
+    <t>FRLMPersonneStructure.personne.identifiantPersonne</t>
   </si>
   <si>
     <t>assignedEntity.id</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.professionRole</t>
+    <t>FRLMPersonneStructure.personne.professionRole</t>
   </si>
   <si>
     <t>assignedEntity.code</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.adresse</t>
+    <t>FRLMPersonneStructure.personne.adresse</t>
   </si>
   <si>
     <t>assignedEntity.addr</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.coordonneesTelecom</t>
+    <t>FRLMPersonneStructure.personne.coordonneesTelecom</t>
   </si>
   <si>
     <t>assignedEntity.telecom</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.IdentitePersonne</t>
+    <t>FRLMPersonneStructure.personne.IdentitePersonne</t>
   </si>
   <si>
     <t>assignedEntity.assignedPerson</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.IdentitePersonne.nomPersonne</t>
+    <t>FRLMPersonneStructure.personne.IdentitePersonne.nomPersonne</t>
   </si>
   <si>
     <t>assignedEntity.assignedPerson.name.family</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.IdentitePersonne.prenomPersonne</t>
+    <t>FRLMPersonneStructure.personne.IdentitePersonne.prenomPersonne</t>
   </si>
   <si>
     <t>assignedEntity.assignedPerson.name.given</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.IdentitePersonne.civilite</t>
+    <t>FRLMPersonneStructure.personne.IdentitePersonne.civilite</t>
   </si>
   <si>
     <t>assignedEntity.assignedPerson.name.prefix</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.IdentitePersonne.titre</t>
+    <t>FRLMPersonneStructure.personne.IdentitePersonne.titre</t>
   </si>
   <si>
     <t>assignedEntity.assignedPerson.name.suffix</t>
   </si>
   <si>
-    <t>PersonneStructure.structure</t>
+    <t>FRLMPersonneStructure.structure</t>
   </si>
   <si>
     <t>assignedEntity.representedOrganization</t>
   </si>
   <si>
-    <t>PersonneStructure.structure.identifiantStructure</t>
+    <t>FRLMPersonneStructure.structure.identifiantStructure</t>
   </si>
   <si>
     <t>assignedEntity.representedOrganization.id</t>
   </si>
   <si>
-    <t>PersonneStructure.structure.nomStructure</t>
+    <t>FRLMPersonneStructure.structure.nomStructure</t>
   </si>
   <si>
     <t>assignedEntity.representedOrganization.name</t>
   </si>
   <si>
-    <t>PersonneStructure.structure.adresse</t>
+    <t>FRLMPersonneStructure.structure.adresse</t>
   </si>
   <si>
     <t>assignedEntity.representedOrganization.addr</t>
   </si>
   <si>
-    <t>PersonneStructure.structure.coordonneesTelecom</t>
+    <t>FRLMPersonneStructure.structure.coordonneesTelecom</t>
   </si>
   <si>
     <t>assignedEntity.representedOrganization.telecom</t>
   </si>
   <si>
-    <t>PersonneStructure.structure.secteurActivite</t>
+    <t>FRLMPersonneStructure.structure.secteurActivite</t>
   </si>
   <si>
     <t>assignedEntity.representedOrganization.standardIndustryClassCode</t>

--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
